--- a/wwwroot/assets/template/Chapter_Template.xlsx
+++ b/wwwroot/assets/template/Chapter_Template.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93152B57-0B36-404F-9FCB-AAB54336D211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chapters" sheetId="1" r:id="rId1"/>
@@ -45,9 +46,6 @@
     <t>Created Date</t>
   </si>
   <si>
-    <t>Bí Ẩn Rừng Sâu</t>
-  </si>
-  <si>
     <t>2025-09-15</t>
   </si>
   <si>
@@ -57,19 +55,22 @@
     <t>2025-08-20</t>
   </si>
   <si>
-    <t>Chạm mặt nhau</t>
-  </si>
-  <si>
-    <t>Chiến đấu không ngừng</t>
-  </si>
-  <si>
-    <t>Không thể gục ngã</t>
+    <t>Simple story</t>
+  </si>
+  <si>
+    <t>Up side down</t>
+  </si>
+  <si>
+    <t>Inside down</t>
+  </si>
+  <si>
+    <t>Out side in</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -398,19 +399,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" customWidth="1"/>
-    <col min="3" max="3" width="17.5703125" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" customWidth="1"/>
+    <col min="3" max="3" width="17.5546875" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="15.42578125" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" customWidth="1"/>
+    <col min="5" max="5" width="15.44140625" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -420,7 +421,7 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -430,7 +431,7 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
@@ -440,7 +441,7 @@
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -457,55 +458,55 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B6">
-        <v>13</v>
+        <v>83</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D6">
         <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7">
-        <v>13</v>
+        <v>83</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D7">
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8">
-        <v>13</v>
+        <v>83</v>
       </c>
       <c r="C8" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D8">
         <v>6</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
